--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/mar-2026.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/mar-2026.xlsx
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>156392.775</v>
+        <v>156392.78</v>
       </c>
     </row>
     <row r="6">
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>102645.592</v>
+        <v>102645.59</v>
       </c>
     </row>
     <row r="17">
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>12754.5747</v>
+        <v>12754.57</v>
       </c>
     </row>
     <row r="24">
@@ -1927,7 +1927,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>12754.5747</v>
+        <v>12754.57</v>
       </c>
     </row>
     <row r="25">
@@ -2842,7 +2842,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>80607.74400000001</v>
+        <v>80607.74000000001</v>
       </c>
     </row>
     <row r="40">
